--- a/output/yearly_total_coral_cover_iteration_56_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_56_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.266843737841165</v>
+        <v>1.253482151586366</v>
       </c>
       <c r="C3" t="n">
-        <v>4.572575235639951</v>
+        <v>4.657565134396597</v>
       </c>
       <c r="D3" t="n">
-        <v>6.208489127036607</v>
+        <v>6.094969639994549</v>
       </c>
       <c r="E3" t="n">
-        <v>12.04790810051772</v>
+        <v>12.00601692597751</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.414913714157512</v>
+        <v>1.38240540708089</v>
       </c>
       <c r="C4" t="n">
-        <v>4.998278268490706</v>
+        <v>5.202165934920209</v>
       </c>
       <c r="D4" t="n">
-        <v>6.507116099748602</v>
+        <v>6.362554594638028</v>
       </c>
       <c r="E4" t="n">
-        <v>12.92030808239682</v>
+        <v>12.94712593663913</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.621067788241535</v>
+        <v>1.560840700978866</v>
       </c>
       <c r="C5" t="n">
-        <v>5.533781401945451</v>
+        <v>5.898891224813627</v>
       </c>
       <c r="D5" t="n">
-        <v>6.858760959576112</v>
+        <v>6.650719463441355</v>
       </c>
       <c r="E5" t="n">
-        <v>14.0136101497631</v>
+        <v>14.11045138923385</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853162216138952</v>
+        <v>1.761137164123159</v>
       </c>
       <c r="C6" t="n">
-        <v>6.192261481842873</v>
+        <v>6.750328812855282</v>
       </c>
       <c r="D6" t="n">
-        <v>7.254985609829248</v>
+        <v>6.962370538931056</v>
       </c>
       <c r="E6" t="n">
-        <v>15.30040930781107</v>
+        <v>15.4738365159095</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.11251554822009</v>
+        <v>1.989882712420532</v>
       </c>
       <c r="C7" t="n">
-        <v>6.958567490506635</v>
+        <v>7.71747384790674</v>
       </c>
       <c r="D7" t="n">
-        <v>7.703665090270571</v>
+        <v>7.298707713490421</v>
       </c>
       <c r="E7" t="n">
-        <v>16.7747481289973</v>
+        <v>17.00606427381769</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.32431044961817</v>
+        <v>1.215711310923955</v>
       </c>
       <c r="C8" t="n">
-        <v>4.621482338264639</v>
+        <v>5.288022384170556</v>
       </c>
       <c r="D8" t="n">
-        <v>5.959020717541462</v>
+        <v>5.469727182389678</v>
       </c>
       <c r="E8" t="n">
-        <v>11.90481350542427</v>
+        <v>11.97346087748419</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.668248725862338</v>
+        <v>1.520185980082328</v>
       </c>
       <c r="C9" t="n">
-        <v>5.579383690741908</v>
+        <v>6.417303591976358</v>
       </c>
       <c r="D9" t="n">
-        <v>6.562613945463228</v>
+        <v>5.909550826478351</v>
       </c>
       <c r="E9" t="n">
-        <v>13.81024636206747</v>
+        <v>13.84704039853704</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.031445941738369</v>
+        <v>1.84034905699537</v>
       </c>
       <c r="C10" t="n">
-        <v>6.678142393595791</v>
+        <v>7.672998171927667</v>
       </c>
       <c r="D10" t="n">
-        <v>7.195134524288274</v>
+        <v>6.340618663965924</v>
       </c>
       <c r="E10" t="n">
-        <v>15.90472285962244</v>
+        <v>15.85396589288896</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.399287764772333</v>
+        <v>2.171211755436483</v>
       </c>
       <c r="C11" t="n">
-        <v>7.915826340527073</v>
+        <v>9.094049120954972</v>
       </c>
       <c r="D11" t="n">
-        <v>7.762723281208369</v>
+        <v>6.770297233274048</v>
       </c>
       <c r="E11" t="n">
-        <v>18.07783738650777</v>
+        <v>18.0355581096655</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.77396783941984</v>
+        <v>2.509294891682457</v>
       </c>
       <c r="C12" t="n">
-        <v>9.284858801042262</v>
+        <v>10.69828135014714</v>
       </c>
       <c r="D12" t="n">
-        <v>8.42300068793956</v>
+        <v>7.151614917107024</v>
       </c>
       <c r="E12" t="n">
-        <v>20.48182732840166</v>
+        <v>20.35919115893662</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.144395500324948</v>
+        <v>2.857425937745423</v>
       </c>
       <c r="C13" t="n">
-        <v>10.70294722124448</v>
+        <v>12.44250810205058</v>
       </c>
       <c r="D13" t="n">
-        <v>9.027862827202584</v>
+        <v>7.548417766203522</v>
       </c>
       <c r="E13" t="n">
-        <v>22.87520554877202</v>
+        <v>22.84835180599953</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.821014364176281</v>
+        <v>1.659615041598106</v>
       </c>
       <c r="C14" t="n">
-        <v>7.604018850996202</v>
+        <v>8.948895396089823</v>
       </c>
       <c r="D14" t="n">
-        <v>6.844637001761295</v>
+        <v>5.72484575282034</v>
       </c>
       <c r="E14" t="n">
-        <v>16.26967021693378</v>
+        <v>16.33335619050827</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.87387166057293</v>
+        <v>1.712452703040669</v>
       </c>
       <c r="C15" t="n">
-        <v>8.230629140708773</v>
+        <v>9.847822864006373</v>
       </c>
       <c r="D15" t="n">
-        <v>6.940239593200849</v>
+        <v>5.672665862339622</v>
       </c>
       <c r="E15" t="n">
-        <v>17.04474039448255</v>
+        <v>17.23294142938666</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.184369006995068</v>
+        <v>1.993075466822577</v>
       </c>
       <c r="C16" t="n">
-        <v>9.767358822166305</v>
+        <v>11.82803743590332</v>
       </c>
       <c r="D16" t="n">
-        <v>7.524919438465037</v>
+        <v>6.003652283349393</v>
       </c>
       <c r="E16" t="n">
-        <v>19.47664726762641</v>
+        <v>19.82476518607529</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.753077423042402</v>
+        <v>1.59833434989902</v>
       </c>
       <c r="C17" t="n">
-        <v>9.091504067608716</v>
+        <v>11.05574560435756</v>
       </c>
       <c r="D17" t="n">
-        <v>7.042095917516456</v>
+        <v>5.493064937324712</v>
       </c>
       <c r="E17" t="n">
-        <v>17.88667740816758</v>
+        <v>18.14714489158129</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.012798778200896</v>
+        <v>1.817460437486908</v>
       </c>
       <c r="C18" t="n">
-        <v>10.61464636083947</v>
+        <v>13.05634125859467</v>
       </c>
       <c r="D18" t="n">
-        <v>7.561607350172741</v>
+        <v>5.833289604231443</v>
       </c>
       <c r="E18" t="n">
-        <v>20.18905248921311</v>
+        <v>20.70709130031302</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.032914788660913</v>
+        <v>1.812433889241164</v>
       </c>
       <c r="C19" t="n">
-        <v>11.36449543986614</v>
+        <v>14.0963262366574</v>
       </c>
       <c r="D19" t="n">
-        <v>7.738793175835206</v>
+        <v>5.856046516015884</v>
       </c>
       <c r="E19" t="n">
-        <v>21.13620340436226</v>
+        <v>21.76480664191445</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.283427350353572</v>
+        <v>2.003216920607447</v>
       </c>
       <c r="C20" t="n">
-        <v>13.05366108736208</v>
+        <v>16.29710024779044</v>
       </c>
       <c r="D20" t="n">
-        <v>8.236686524043975</v>
+        <v>6.185854839780558</v>
       </c>
       <c r="E20" t="n">
-        <v>23.57377496175963</v>
+        <v>24.48617200817844</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.372817084756485</v>
+        <v>1.182956896232194</v>
       </c>
       <c r="C21" t="n">
-        <v>9.602101231110439</v>
+        <v>12.05366269329332</v>
       </c>
       <c r="D21" t="n">
-        <v>6.896689265040461</v>
+        <v>5.10483280768031</v>
       </c>
       <c r="E21" t="n">
-        <v>17.87160758090738</v>
+        <v>18.34145239720582</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_56_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_56_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.253482151586366</v>
+        <v>1.252353141726482</v>
       </c>
       <c r="C3" t="n">
-        <v>4.657565134396597</v>
+        <v>4.640090025261004</v>
       </c>
       <c r="D3" t="n">
-        <v>6.094969639994549</v>
+        <v>6.140100581958775</v>
       </c>
       <c r="E3" t="n">
-        <v>12.00601692597751</v>
+        <v>12.03254374894626</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.38240540708089</v>
+        <v>1.371002770109355</v>
       </c>
       <c r="C4" t="n">
-        <v>5.202165934920209</v>
+        <v>5.173121672480002</v>
       </c>
       <c r="D4" t="n">
-        <v>6.362554594638028</v>
+        <v>6.386979942681426</v>
       </c>
       <c r="E4" t="n">
-        <v>12.94712593663913</v>
+        <v>12.93110438527078</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.560840700978866</v>
+        <v>1.529422605077805</v>
       </c>
       <c r="C5" t="n">
-        <v>5.898891224813627</v>
+        <v>5.865293533077278</v>
       </c>
       <c r="D5" t="n">
-        <v>6.650719463441355</v>
+        <v>6.758671984291879</v>
       </c>
       <c r="E5" t="n">
-        <v>14.11045138923385</v>
+        <v>14.15338812244696</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.761137164123159</v>
+        <v>1.699688638929598</v>
       </c>
       <c r="C6" t="n">
-        <v>6.750328812855282</v>
+        <v>6.730667530121562</v>
       </c>
       <c r="D6" t="n">
-        <v>6.962370538931056</v>
+        <v>7.091811285270548</v>
       </c>
       <c r="E6" t="n">
-        <v>15.4738365159095</v>
+        <v>15.52216745432171</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.989882712420532</v>
+        <v>1.884853722776294</v>
       </c>
       <c r="C7" t="n">
-        <v>7.71747384790674</v>
+        <v>7.754818310391745</v>
       </c>
       <c r="D7" t="n">
-        <v>7.298707713490421</v>
+        <v>7.548172537550576</v>
       </c>
       <c r="E7" t="n">
-        <v>17.00606427381769</v>
+        <v>17.18784457071861</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.215711310923955</v>
+        <v>1.115129088794276</v>
       </c>
       <c r="C8" t="n">
-        <v>5.288022384170556</v>
+        <v>5.404615404194244</v>
       </c>
       <c r="D8" t="n">
-        <v>5.469727182389678</v>
+        <v>5.776293727482074</v>
       </c>
       <c r="E8" t="n">
-        <v>11.97346087748419</v>
+        <v>12.29603822047059</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.520185980082328</v>
+        <v>1.386881764869241</v>
       </c>
       <c r="C9" t="n">
-        <v>6.417303591976358</v>
+        <v>6.671196286363145</v>
       </c>
       <c r="D9" t="n">
-        <v>5.909550826478351</v>
+        <v>6.260310216673071</v>
       </c>
       <c r="E9" t="n">
-        <v>13.84704039853704</v>
+        <v>14.31838826790546</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.84034905699537</v>
+        <v>1.674703629250419</v>
       </c>
       <c r="C10" t="n">
-        <v>7.672998171927667</v>
+        <v>8.157042001551456</v>
       </c>
       <c r="D10" t="n">
-        <v>6.340618663965924</v>
+        <v>6.745959547581101</v>
       </c>
       <c r="E10" t="n">
-        <v>15.85396589288896</v>
+        <v>16.57770517838298</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.171211755436483</v>
+        <v>1.962004021157062</v>
       </c>
       <c r="C11" t="n">
-        <v>9.094049120954972</v>
+        <v>9.766343651842339</v>
       </c>
       <c r="D11" t="n">
-        <v>6.770297233274048</v>
+        <v>7.20298560046232</v>
       </c>
       <c r="E11" t="n">
-        <v>18.0355581096655</v>
+        <v>18.93133327346172</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.509294891682457</v>
+        <v>2.253342329593799</v>
       </c>
       <c r="C12" t="n">
-        <v>10.69828135014714</v>
+        <v>11.51122048091893</v>
       </c>
       <c r="D12" t="n">
-        <v>7.151614917107024</v>
+        <v>7.668534505129948</v>
       </c>
       <c r="E12" t="n">
-        <v>20.35919115893662</v>
+        <v>21.43309731564268</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.857425937745423</v>
+        <v>2.52365517810899</v>
       </c>
       <c r="C13" t="n">
-        <v>12.44250810205058</v>
+        <v>13.28803742533776</v>
       </c>
       <c r="D13" t="n">
-        <v>7.548417766203522</v>
+        <v>8.115372028995758</v>
       </c>
       <c r="E13" t="n">
-        <v>22.84835180599953</v>
+        <v>23.92706463244251</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.659615041598106</v>
+        <v>1.455499876408151</v>
       </c>
       <c r="C14" t="n">
-        <v>8.948895396089823</v>
+        <v>9.31790490568507</v>
       </c>
       <c r="D14" t="n">
-        <v>5.72484575282034</v>
+        <v>6.120578434925187</v>
       </c>
       <c r="E14" t="n">
-        <v>16.33335619050827</v>
+        <v>16.89398321701841</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.712452703040669</v>
+        <v>1.478070256128786</v>
       </c>
       <c r="C15" t="n">
-        <v>9.847822864006373</v>
+        <v>10.17820060143951</v>
       </c>
       <c r="D15" t="n">
-        <v>5.672665862339622</v>
+        <v>6.099510129192051</v>
       </c>
       <c r="E15" t="n">
-        <v>17.23294142938666</v>
+        <v>17.75578098676035</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.993075466822577</v>
+        <v>1.709654722083565</v>
       </c>
       <c r="C16" t="n">
-        <v>11.82803743590332</v>
+        <v>12.11618038709976</v>
       </c>
       <c r="D16" t="n">
-        <v>6.003652283349393</v>
+        <v>6.547913575629739</v>
       </c>
       <c r="E16" t="n">
-        <v>19.82476518607529</v>
+        <v>20.37374868481306</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.59833434989902</v>
+        <v>1.371481907878709</v>
       </c>
       <c r="C17" t="n">
-        <v>11.05574560435756</v>
+        <v>11.23611229258179</v>
       </c>
       <c r="D17" t="n">
-        <v>5.493064937324712</v>
+        <v>6.046986627014847</v>
       </c>
       <c r="E17" t="n">
-        <v>18.14714489158129</v>
+        <v>18.65458082747534</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.817460437486908</v>
+        <v>1.562883440298668</v>
       </c>
       <c r="C18" t="n">
-        <v>13.05634125859467</v>
+        <v>13.20485023381609</v>
       </c>
       <c r="D18" t="n">
-        <v>5.833289604231443</v>
+        <v>6.430712534696755</v>
       </c>
       <c r="E18" t="n">
-        <v>20.70709130031302</v>
+        <v>21.19844620881151</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.812433889241164</v>
+        <v>1.563639386030937</v>
       </c>
       <c r="C19" t="n">
-        <v>14.0963262366574</v>
+        <v>14.20170703523126</v>
       </c>
       <c r="D19" t="n">
-        <v>5.856046516015884</v>
+        <v>6.488282220073788</v>
       </c>
       <c r="E19" t="n">
-        <v>21.76480664191445</v>
+        <v>22.25362864133598</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.003216920607447</v>
+        <v>1.727718879841707</v>
       </c>
       <c r="C20" t="n">
-        <v>16.29710024779044</v>
+        <v>16.33929576411896</v>
       </c>
       <c r="D20" t="n">
-        <v>6.185854839780558</v>
+        <v>6.914792692706773</v>
       </c>
       <c r="E20" t="n">
-        <v>24.48617200817844</v>
+        <v>24.98180733666744</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.182956896232194</v>
+        <v>1.022814210715455</v>
       </c>
       <c r="C21" t="n">
-        <v>12.05366269329332</v>
+        <v>12.02852013458756</v>
       </c>
       <c r="D21" t="n">
-        <v>5.10483280768031</v>
+        <v>5.741024954986329</v>
       </c>
       <c r="E21" t="n">
-        <v>18.34145239720582</v>
+        <v>18.79235930028934</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_56_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_56_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.252353141726482</v>
+        <v>2.58071971203712</v>
       </c>
       <c r="C3" t="n">
-        <v>4.640090025261004</v>
+        <v>7.66408916237557</v>
       </c>
       <c r="D3" t="n">
-        <v>6.140100581958775</v>
+        <v>8.254738669382496</v>
       </c>
       <c r="E3" t="n">
-        <v>12.03254374894626</v>
+        <v>18.49954754379518</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.371002770109355</v>
+        <v>1.050676165479226</v>
       </c>
       <c r="C4" t="n">
-        <v>5.173121672480002</v>
+        <v>4.385417676060493</v>
       </c>
       <c r="D4" t="n">
-        <v>6.386979942681426</v>
+        <v>6.00299450938203</v>
       </c>
       <c r="E4" t="n">
-        <v>12.93110438527078</v>
+        <v>11.43908835092175</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.529422605077805</v>
+        <v>1.13383918727243</v>
       </c>
       <c r="C5" t="n">
-        <v>5.865293533077278</v>
+        <v>4.917223036023757</v>
       </c>
       <c r="D5" t="n">
-        <v>6.758671984291879</v>
+        <v>6.445458860205391</v>
       </c>
       <c r="E5" t="n">
-        <v>14.15338812244696</v>
+        <v>12.49652108350158</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.699688638929598</v>
+        <v>1.233865732797682</v>
       </c>
       <c r="C6" t="n">
-        <v>6.730667530121562</v>
+        <v>5.582463068824339</v>
       </c>
       <c r="D6" t="n">
-        <v>7.091811285270548</v>
+        <v>7.01198331261824</v>
       </c>
       <c r="E6" t="n">
-        <v>15.52216745432171</v>
+        <v>13.82831211424026</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.884853722776294</v>
+        <v>1.335756097196606</v>
       </c>
       <c r="C7" t="n">
-        <v>7.754818310391745</v>
+        <v>6.38008734850411</v>
       </c>
       <c r="D7" t="n">
-        <v>7.548172537550576</v>
+        <v>7.563016930723983</v>
       </c>
       <c r="E7" t="n">
-        <v>17.18784457071861</v>
+        <v>15.2788603764247</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.115129088794276</v>
+        <v>1.447512588274977</v>
       </c>
       <c r="C8" t="n">
-        <v>5.404615404194244</v>
+        <v>7.272653298420881</v>
       </c>
       <c r="D8" t="n">
-        <v>5.776293727482074</v>
+        <v>8.086769775411813</v>
       </c>
       <c r="E8" t="n">
-        <v>12.29603822047059</v>
+        <v>16.80693566210767</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.386881764869241</v>
+        <v>1.56109973966604</v>
       </c>
       <c r="C9" t="n">
-        <v>6.671196286363145</v>
+        <v>8.31939744947594</v>
       </c>
       <c r="D9" t="n">
-        <v>6.260310216673071</v>
+        <v>8.705467725385695</v>
       </c>
       <c r="E9" t="n">
-        <v>14.31838826790546</v>
+        <v>18.58596491452768</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.674703629250419</v>
+        <v>0.9864011883649402</v>
       </c>
       <c r="C10" t="n">
-        <v>8.157042001551456</v>
+        <v>6.252466421513703</v>
       </c>
       <c r="D10" t="n">
-        <v>6.745959547581101</v>
+        <v>6.882640455392688</v>
       </c>
       <c r="E10" t="n">
-        <v>16.57770517838298</v>
+        <v>14.12150806527133</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.962004021157062</v>
+        <v>0.9152637497152164</v>
       </c>
       <c r="C11" t="n">
-        <v>9.766343651842339</v>
+        <v>6.529427266358772</v>
       </c>
       <c r="D11" t="n">
-        <v>7.20298560046232</v>
+        <v>6.886557628732633</v>
       </c>
       <c r="E11" t="n">
-        <v>18.93133327346172</v>
+        <v>14.33124864480662</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.253342329593799</v>
+        <v>0.9783017698049041</v>
       </c>
       <c r="C12" t="n">
-        <v>11.51122048091893</v>
+        <v>7.710538476906982</v>
       </c>
       <c r="D12" t="n">
-        <v>7.668534505129948</v>
+        <v>7.432026470689205</v>
       </c>
       <c r="E12" t="n">
-        <v>21.43309731564268</v>
+        <v>16.12086671740109</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.52365517810899</v>
+        <v>0.7704854157699393</v>
       </c>
       <c r="C13" t="n">
-        <v>13.28803742533776</v>
+        <v>7.404753519465227</v>
       </c>
       <c r="D13" t="n">
-        <v>8.115372028995758</v>
+        <v>6.9234909773664</v>
       </c>
       <c r="E13" t="n">
-        <v>23.92706463244251</v>
+        <v>15.09872991260157</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.455499876408151</v>
+        <v>0.827377695231042</v>
       </c>
       <c r="C14" t="n">
-        <v>9.31790490568507</v>
+        <v>8.728394861715989</v>
       </c>
       <c r="D14" t="n">
-        <v>6.120578434925187</v>
+        <v>7.432075558074417</v>
       </c>
       <c r="E14" t="n">
-        <v>16.89398321701841</v>
+        <v>16.98784811502145</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.478070256128786</v>
+        <v>0.7955985220445727</v>
       </c>
       <c r="C15" t="n">
-        <v>10.17820060143951</v>
+        <v>9.50091249523372</v>
       </c>
       <c r="D15" t="n">
-        <v>6.099510129192051</v>
+        <v>7.588075268279234</v>
       </c>
       <c r="E15" t="n">
-        <v>17.75578098676035</v>
+        <v>17.88458628555753</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.709654722083565</v>
+        <v>0.8636925428111314</v>
       </c>
       <c r="C16" t="n">
-        <v>12.11618038709976</v>
+        <v>11.20977200167684</v>
       </c>
       <c r="D16" t="n">
-        <v>6.547913575629739</v>
+        <v>8.13077558170983</v>
       </c>
       <c r="E16" t="n">
-        <v>20.37374868481306</v>
+        <v>20.20424012619781</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.371481907878709</v>
+        <v>0.5184315101816133</v>
       </c>
       <c r="C17" t="n">
-        <v>11.23611229258179</v>
+        <v>8.581289785711649</v>
       </c>
       <c r="D17" t="n">
-        <v>6.046986627014847</v>
+        <v>6.82616050996737</v>
       </c>
       <c r="E17" t="n">
-        <v>18.65458082747534</v>
+        <v>15.92588180586063</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.562883440298668</v>
+        <v>0.3975587328347459</v>
       </c>
       <c r="C18" t="n">
-        <v>13.20485023381609</v>
+        <v>7.776237033275179</v>
       </c>
       <c r="D18" t="n">
-        <v>6.430712534696755</v>
+        <v>6.330093212488499</v>
       </c>
       <c r="E18" t="n">
-        <v>21.19844620881151</v>
+        <v>14.50388897859842</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.563639386030937</v>
+        <v>0.4586921623781948</v>
       </c>
       <c r="C19" t="n">
-        <v>14.20170703523126</v>
+        <v>9.688917180596984</v>
       </c>
       <c r="D19" t="n">
-        <v>6.488282220073788</v>
+        <v>6.908205165611276</v>
       </c>
       <c r="E19" t="n">
-        <v>22.25362864133598</v>
+        <v>17.05581450858645</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.727718879841707</v>
+        <v>0.5168705313318608</v>
       </c>
       <c r="C20" t="n">
-        <v>16.33929576411896</v>
+        <v>11.70337511241806</v>
       </c>
       <c r="D20" t="n">
-        <v>6.914792692706773</v>
+        <v>7.515897177063009</v>
       </c>
       <c r="E20" t="n">
-        <v>24.98180733666744</v>
+        <v>19.73614282081293</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.022814210715455</v>
+        <v>0.5673421808071892</v>
       </c>
       <c r="C21" t="n">
-        <v>12.02852013458756</v>
+        <v>13.80572891620035</v>
       </c>
       <c r="D21" t="n">
-        <v>5.741024954986329</v>
+        <v>8.084034573510641</v>
       </c>
       <c r="E21" t="n">
-        <v>18.79235930028934</v>
+        <v>22.45710567051817</v>
       </c>
     </row>
   </sheetData>
